--- a/data/comments/comments_manual_coding.xlsx
+++ b/data/comments/comments_manual_coding.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joellattmann/Documents/GitHub/like_dislike/data/comments/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuginkha/Documents/Mediapsychology/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C29023-2BF9-4546-A641-338CE6211489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D6CD28-95C9-634C-BA36-DBFBB33F6CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C1BB1A16-32F0-7443-88B2-C6116B7B62A9}"/>
   </bookViews>
@@ -1632,7 +1632,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1640,18 +1640,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1671,7 +1681,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2100,7 +2110,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -2268,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -2346,19 +2356,19 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
         <v>42</v>
@@ -2397,13 +2407,13 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>2</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="s">
         <v>47</v>
@@ -2442,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2475,10 +2485,10 @@
         <v>52</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2487,10 +2497,10 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="s">
         <v>53</v>
@@ -2577,10 +2587,10 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
         <v>61</v>
@@ -2610,19 +2620,19 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
         <v>64</v>
@@ -2658,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>3</v>
@@ -2703,7 +2713,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>3</v>
@@ -2748,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="s">
         <v>75</v>
@@ -2787,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -2832,7 +2842,7 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -2874,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>4</v>
@@ -2892,7 +2902,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2909,22 +2919,22 @@
       <c r="E21" t="s">
         <v>87</v>
       </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>3</v>
+      </c>
+      <c r="K21" s="2">
         <v>0</v>
       </c>
       <c r="L21" t="s">
@@ -3197,7 +3207,7 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>27</v>
       </c>
       <c r="B28">
@@ -3219,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>2</v>
@@ -4119,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>2</v>
@@ -4533,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -4635,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60">
         <v>2</v>
@@ -4929,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>2</v>
@@ -5082,7 +5092,7 @@
         <v>2</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="s">
         <v>246</v>
@@ -5118,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -5130,7 +5140,7 @@
         <v>2</v>
       </c>
       <c r="K70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>249</v>
@@ -5271,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -5319,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J74">
         <v>3</v>
@@ -5520,7 +5530,7 @@
         <v>2</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="s">
         <v>272</v>
@@ -5616,10 +5626,10 @@
         <v>2</v>
       </c>
       <c r="J80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="s">
         <v>278</v>
@@ -6240,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J93">
         <v>2</v>
@@ -6576,13 +6586,13 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100">
         <v>2</v>
       </c>
       <c r="J100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -6627,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101">
         <v>4</v>
@@ -6936,7 +6946,7 @@
         <v>365</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -6948,7 +6958,7 @@
         <v>4</v>
       </c>
       <c r="J107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -7212,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112">
         <v>1</v>
@@ -7266,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -7329,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -7812,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123">
         <v>2</v>
       </c>
       <c r="J123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="s">
         <v>424</v>
@@ -8034,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127">
         <v>3</v>
@@ -8088,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128">
         <v>1</v>
@@ -8463,13 +8473,13 @@
         <v>0</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135">
         <v>1</v>
       </c>
       <c r="I135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135">
         <v>2</v>
@@ -8634,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -9009,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145">
         <v>2</v>
@@ -9234,7 +9244,7 @@
         <v>0</v>
       </c>
       <c r="J149">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -9342,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K151">
         <v>0</v>

--- a/data/comments/comments_manual_coding.xlsx
+++ b/data/comments/comments_manual_coding.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuginkha/Documents/Mediapsychology/like_dislike/data/comments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D6CD28-95C9-634C-BA36-DBFBB33F6CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3DA385-9A47-614D-B00A-B8EDA45669C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C1BB1A16-32F0-7443-88B2-C6116B7B62A9}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,8 @@
   <definedNames>
     <definedName name="comments_reliy_coded" localSheetId="0">Sheet1!$A$1:$T$151</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,47 +31,19 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{33EC562D-7260-BB47-9F86-36B2340BEF71}" name="comments_reliy_coded" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/yuginkha/Documents/Mediapsychology/like_dislike/data/comments/comments_reliy_coded.csv" thousands="'" tab="0" comma="1">
-      <textFields count="20">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="512">
   <si>
+    <t>unique_id</t>
+  </si>
+  <si>
     <t>post_number</t>
   </si>
   <si>
@@ -1606,9 +1575,6 @@
   </si>
   <si>
     <t>&lt;div class=wrap&gt;&lt;img src="/uploads/default/original/1X/b66a6075fd4037d5b392e37ba70d7b8cc4887798.jpg" width="690" height="244"&gt;&lt;/div&gt; Der Neun-Punkte-Plan wurde in den Medien und in der Bevölkerung viel diskutiert. Uns interessiert: Wie würden Sie ihn genau bewerten, was wären Wörter, mit denen Sie ihn beschreiben können? ## Stimmen Sie jetzt ab! Ich finde den Neun-Punkte-Plan ... [poll type=regular max=20] * gut * schlecht [/poll] [poll name=poll2 type=regular] * Nutzlos * Nützlich [/poll] [poll name=poll3 type=regular] * Unüberlegt * Überlegt [/poll] [poll name=poll4 type=regular] * Beunruhigend * Beruhigend [/poll] [poll name=poll5 type=regular] * Unangenehm * Angenehm [/poll]</t>
-  </si>
-  <si>
-    <t>unique_id</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1587,7 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1645,7 +1611,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1676,19 +1642,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="comments_reliy_coded" connectionId="1" xr16:uid="{0809363D-BB62-EB46-8BED-40B4C575B588}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -1726,150 +1688,52 @@
         <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -1877,33 +1741,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -1916,13 +1771,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1932,15 +1781,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -1948,7 +1795,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -1956,149 +1802,124 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD865AD-3321-FD44-A323-C33773778A6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="48.83203125" customWidth="1"/>
     <col min="5" max="5" width="38.6640625" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="80.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="5.5" customWidth="1"/>
+    <col min="12" max="12" width="19.5" customWidth="1"/>
+    <col min="13" max="13" width="19.1640625" customWidth="1"/>
+    <col min="14" max="14" width="80.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.83203125" customWidth="1"/>
+    <col min="16" max="16" width="39.5" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" customWidth="1"/>
+    <col min="18" max="18" width="80.6640625" customWidth="1"/>
+    <col min="19" max="19" width="8.5" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>511</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2119,28 +1940,28 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3">
         <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -2161,10 +1982,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2176,13 +1997,13 @@
         <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2203,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2218,13 +2039,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2245,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2260,13 +2081,13 @@
         <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2287,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2302,13 +2123,13 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2329,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2344,13 +2165,13 @@
         <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2371,13 +2192,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8">
         <v>147</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2389,13 +2210,13 @@
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2416,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2431,13 +2252,13 @@
         <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2458,13 +2279,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M10">
         <v>44</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2476,13 +2297,13 @@
         <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -2503,13 +2324,13 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M11">
         <v>32</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2521,13 +2342,13 @@
         <v>167</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2548,13 +2369,13 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M12">
         <v>156</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2566,13 +2387,13 @@
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2593,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2608,13 +2429,13 @@
         <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2635,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M14">
         <v>2</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2653,13 +2474,13 @@
         <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2680,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2695,13 +2516,13 @@
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2722,10 +2543,10 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2737,13 +2558,13 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2764,10 +2585,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2779,13 +2600,13 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2806,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M18">
         <v>34</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2824,13 +2645,13 @@
         <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2851,13 +2672,13 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M19">
         <v>69</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2869,13 +2690,13 @@
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2896,13 +2717,13 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2911,13 +2732,13 @@
         <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
@@ -2938,10 +2759,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2953,13 +2774,13 @@
         <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2980,10 +2801,10 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2995,13 +2816,13 @@
         <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -3010,25 +2831,25 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>2</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K23">
         <v>0</v>
       </c>
       <c r="L23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M23">
         <v>116</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3040,13 +2861,13 @@
         <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -3067,13 +2888,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M24">
         <v>74</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3085,13 +2906,13 @@
         <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -3112,10 +2933,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3127,13 +2948,13 @@
         <v>190</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -3154,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M26">
         <v>187</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3172,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -3199,28 +3020,28 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f>ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28">
         <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -3241,10 +3062,10 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3256,13 +3077,13 @@
         <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29">
         <v>0</v>
@@ -3283,13 +3104,13 @@
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3301,13 +3122,13 @@
         <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -3328,13 +3149,13 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M30">
         <v>73</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3346,13 +3167,13 @@
         <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3373,10 +3194,10 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3388,13 +3209,13 @@
         <v>142</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3415,10 +3236,10 @@
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3430,13 +3251,13 @@
         <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3457,28 +3278,28 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A34:A65" si="1">ROW()-1</f>
         <v>33</v>
       </c>
       <c r="B34">
         <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -3499,31 +3320,31 @@
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M34">
         <v>167</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B35">
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3544,31 +3365,31 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M35">
         <v>10</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B36">
         <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3583,34 +3404,34 @@
         <v>2</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B37">
         <v>154</v>
       </c>
       <c r="C37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3625,34 +3446,34 @@
         <v>1</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B38">
         <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -3661,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -3673,31 +3494,31 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M38">
         <v>77</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B39">
         <v>28</v>
       </c>
       <c r="C39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3718,28 +3539,28 @@
         <v>0</v>
       </c>
       <c r="L39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B40">
         <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -3760,31 +3581,31 @@
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M40">
         <v>155</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3805,28 +3626,28 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B42">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3847,28 +3668,28 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -3889,28 +3710,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B44">
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -3931,28 +3752,28 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3973,28 +3794,28 @@
         <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B46">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -4009,34 +3830,34 @@
         <v>0</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B47">
         <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -4057,28 +3878,28 @@
         <v>0</v>
       </c>
       <c r="L47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B48">
         <v>77</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -4099,28 +3920,28 @@
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B49">
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -4141,28 +3962,28 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="B50">
         <v>36</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -4183,31 +4004,31 @@
         <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M50">
         <v>4</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B51">
         <v>66</v>
       </c>
       <c r="C51" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4228,28 +4049,28 @@
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B52">
         <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -4258,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -4270,34 +4091,34 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B53">
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -4318,34 +4139,34 @@
         <v>0</v>
       </c>
       <c r="L53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B54">
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -4366,34 +4187,34 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B55">
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -4414,34 +4235,34 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O55" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="B56">
         <v>38</v>
       </c>
       <c r="C56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E56" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4456,40 +4277,40 @@
         <v>1</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K56">
         <v>0</v>
       </c>
       <c r="L56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B57">
         <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E57" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -4510,34 +4331,34 @@
         <v>1</v>
       </c>
       <c r="L57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="B58">
         <v>36</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -4558,34 +4379,34 @@
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="B59">
         <v>34</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E59" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -4606,34 +4427,34 @@
         <v>0</v>
       </c>
       <c r="L59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="B60">
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E60" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -4654,37 +4475,37 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M60">
         <v>4</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="B61">
         <v>57</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D61" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -4705,37 +4526,37 @@
         <v>0</v>
       </c>
       <c r="L61" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M61">
         <v>36</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B62">
         <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D62" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E62" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4756,34 +4577,34 @@
         <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="B63">
         <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D63" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -4804,34 +4625,34 @@
         <v>1</v>
       </c>
       <c r="L63" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O63" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="B64">
         <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4852,37 +4673,37 @@
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M64">
         <v>18</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="B65">
         <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D65" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E65" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4903,34 +4724,34 @@
         <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A66:A97" si="2">ROW()-1</f>
         <v>65</v>
       </c>
       <c r="B66">
         <v>46</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E66" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4951,34 +4772,34 @@
         <v>0</v>
       </c>
       <c r="L66" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67">
-        <f t="shared" ref="A67:A130" si="1">ROW()-1</f>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="B67">
         <v>52</v>
       </c>
       <c r="C67" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D67" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4999,34 +4820,34 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>67</v>
       </c>
       <c r="B68">
         <v>6</v>
       </c>
       <c r="C68" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E68" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -5047,34 +4868,34 @@
         <v>0</v>
       </c>
       <c r="L68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O68" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="B69">
         <v>28</v>
       </c>
       <c r="C69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D69" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E69" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -5095,34 +4916,34 @@
         <v>1</v>
       </c>
       <c r="L69" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="B70">
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D70" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E70" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -5143,37 +4964,37 @@
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M70">
         <v>65</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="B71">
         <v>7</v>
       </c>
       <c r="C71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D71" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E71" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -5194,34 +5015,34 @@
         <v>1</v>
       </c>
       <c r="L71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O71" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P71" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="B72">
         <v>19</v>
       </c>
       <c r="C72" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E72" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -5242,34 +5063,34 @@
         <v>1</v>
       </c>
       <c r="L72" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="B73">
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D73" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -5290,34 +5111,34 @@
         <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="B74">
         <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5338,34 +5159,34 @@
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
       <c r="C75" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D75" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E75" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -5386,34 +5207,34 @@
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B76">
         <v>9</v>
       </c>
       <c r="C76" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E76" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -5434,34 +5255,34 @@
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="B77">
         <v>17</v>
       </c>
       <c r="C77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E77" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5482,37 +5303,37 @@
         <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M77">
         <v>2</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="B78">
         <v>56</v>
       </c>
       <c r="C78" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D78" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E78" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -5533,34 +5354,34 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="B79">
         <v>32</v>
       </c>
       <c r="C79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D79" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E79" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -5581,37 +5402,37 @@
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M79">
         <v>2</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="B80">
         <v>21</v>
       </c>
       <c r="C80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D80" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5620,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>2</v>
@@ -5632,34 +5453,34 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O80" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P80" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="B81">
         <v>28</v>
       </c>
       <c r="C81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5680,34 +5501,34 @@
         <v>0</v>
       </c>
       <c r="L81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="B82">
         <v>34</v>
       </c>
       <c r="C82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D82" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -5722,40 +5543,40 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K82">
         <v>0</v>
       </c>
       <c r="L82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="B83">
         <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D83" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E83" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -5776,34 +5597,34 @@
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="B84">
         <v>89</v>
       </c>
       <c r="C84" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D84" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E84" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -5824,34 +5645,34 @@
         <v>1</v>
       </c>
       <c r="L84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B85">
         <v>90</v>
       </c>
       <c r="C85" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D85" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E85" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5872,34 +5693,34 @@
         <v>1</v>
       </c>
       <c r="L85" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B86">
         <v>42</v>
       </c>
       <c r="C86" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E86" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -5920,37 +5741,37 @@
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M86">
         <v>4</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B87">
         <v>9</v>
       </c>
       <c r="C87" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D87" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E87" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5971,34 +5792,34 @@
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="B88">
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D88" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E88" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -6019,34 +5840,34 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P88" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="B89">
         <v>47</v>
       </c>
       <c r="C89" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D89" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E89" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -6067,34 +5888,34 @@
         <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B90">
         <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E90" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -6115,34 +5936,34 @@
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="B91">
         <v>8</v>
       </c>
       <c r="C91" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D91" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E91" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -6163,34 +5984,34 @@
         <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="B92">
         <v>81</v>
       </c>
       <c r="C92" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E92" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -6211,34 +6032,34 @@
         <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O92" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P92" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B93">
         <v>65</v>
       </c>
       <c r="C93" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D93" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E93" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -6247,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93">
         <v>3</v>
@@ -6259,34 +6080,34 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="B94">
         <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D94" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E94" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -6307,37 +6128,37 @@
         <v>1</v>
       </c>
       <c r="L94" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M94">
         <v>2</v>
       </c>
       <c r="N94" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="B95">
         <v>35</v>
       </c>
       <c r="C95" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E95" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -6358,34 +6179,34 @@
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="B96">
         <v>32</v>
       </c>
       <c r="C96" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D96" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E96" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -6406,34 +6227,34 @@
         <v>1</v>
       </c>
       <c r="L96" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="B97">
         <v>61</v>
       </c>
       <c r="C97" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D97" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E97" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -6454,34 +6275,34 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A98:A129" si="3">ROW()-1</f>
         <v>97</v>
       </c>
       <c r="B98">
         <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D98" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E98" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -6496,40 +6317,40 @@
         <v>3</v>
       </c>
       <c r="J98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O98" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P98" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="B99">
         <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D99" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E99" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6550,34 +6371,34 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>99</v>
       </c>
       <c r="B100">
         <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D100" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E100" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -6598,34 +6419,34 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="B101">
         <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E101" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -6646,34 +6467,34 @@
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>101</v>
       </c>
       <c r="B102">
         <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D102" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E102" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -6694,40 +6515,40 @@
         <v>0</v>
       </c>
       <c r="L102" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T102" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>102</v>
       </c>
       <c r="B103">
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D103" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E103" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -6748,40 +6569,40 @@
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T103" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>103</v>
       </c>
       <c r="B104">
         <v>31</v>
       </c>
       <c r="C104" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D104" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -6796,46 +6617,46 @@
         <v>2</v>
       </c>
       <c r="J104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K104">
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q104" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R104" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T104" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>104</v>
       </c>
       <c r="B105">
         <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -6856,40 +6677,40 @@
         <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q105" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R105" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T105" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="B106">
         <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E106" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -6910,40 +6731,40 @@
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T106" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>106</v>
       </c>
       <c r="B107">
         <v>14</v>
       </c>
       <c r="C107" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E107" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -6964,40 +6785,40 @@
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q107" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R107" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>107</v>
       </c>
       <c r="B108">
         <v>26</v>
       </c>
       <c r="C108" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E108" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -7018,40 +6839,40 @@
         <v>1</v>
       </c>
       <c r="L108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T108" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>108</v>
       </c>
       <c r="B109">
         <v>14</v>
       </c>
       <c r="C109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D109" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -7072,40 +6893,40 @@
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>109</v>
       </c>
       <c r="B110">
         <v>113</v>
       </c>
       <c r="C110" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E110" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -7126,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T110" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D111" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E111" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -7180,40 +7001,40 @@
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R111" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="S111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T111" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>111</v>
       </c>
       <c r="B112">
         <v>73</v>
       </c>
       <c r="C112" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E112" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -7234,43 +7055,43 @@
         <v>1</v>
       </c>
       <c r="L112" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M112">
         <v>50</v>
       </c>
       <c r="N112" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R112" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S112" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T112" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="113" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>112</v>
       </c>
       <c r="B113">
         <v>6</v>
       </c>
       <c r="C113" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E113" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -7291,43 +7112,43 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M113">
         <v>2</v>
       </c>
       <c r="N113" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q113" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R113" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="S113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T113" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>113</v>
       </c>
       <c r="B114">
         <v>29</v>
       </c>
       <c r="C114" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D114" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E114" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -7348,40 +7169,40 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q114" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R114" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T114" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>114</v>
       </c>
       <c r="B115">
         <v>50</v>
       </c>
       <c r="C115" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D115" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E115" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -7402,40 +7223,40 @@
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q115" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R115" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="S115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T115" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>115</v>
       </c>
       <c r="B116">
         <v>15</v>
       </c>
       <c r="C116" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E116" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -7456,40 +7277,40 @@
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M116" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q116" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R116" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="S116" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T116" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>116</v>
       </c>
       <c r="B117">
         <v>101</v>
       </c>
       <c r="C117" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D117" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E117" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -7510,40 +7331,40 @@
         <v>1</v>
       </c>
       <c r="L117" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T117" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>117</v>
       </c>
       <c r="B118">
         <v>26</v>
       </c>
       <c r="C118" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D118" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E118" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -7552,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118">
         <v>1</v>
@@ -7564,40 +7385,40 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="119" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>118</v>
       </c>
       <c r="B119">
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D119" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E119" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -7618,40 +7439,40 @@
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q119" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R119" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>119</v>
       </c>
       <c r="B120">
         <v>24</v>
       </c>
       <c r="C120" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D120" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E120" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -7672,40 +7493,40 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T120" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="B121">
         <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D121" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E121" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -7726,40 +7547,40 @@
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M121" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q121" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R121" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="S121" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T121" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>121</v>
       </c>
       <c r="B122">
         <v>27</v>
       </c>
       <c r="C122" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D122" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E122" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -7780,40 +7601,40 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M122" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q122" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R122" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S122" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T122" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>122</v>
       </c>
       <c r="B123">
         <v>11</v>
       </c>
       <c r="C123" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D123" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E123" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -7834,40 +7655,40 @@
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M123" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q123" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R123" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="S123" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T123" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>123</v>
       </c>
       <c r="B124">
         <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E124" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -7888,40 +7709,40 @@
         <v>1</v>
       </c>
       <c r="L124" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T124" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>124</v>
       </c>
       <c r="B125">
         <v>63</v>
       </c>
       <c r="C125" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D125" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E125" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -7942,40 +7763,40 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M125" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q125" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R125" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="S125" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T125" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>125</v>
       </c>
       <c r="B126">
         <v>90</v>
       </c>
       <c r="C126" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E126" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -7996,43 +7817,43 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M126">
         <v>2</v>
       </c>
       <c r="N126" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T126" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="B127">
         <v>15</v>
       </c>
       <c r="C127" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E127" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -8053,40 +7874,40 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q127" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R127" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="S127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T127" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>127</v>
       </c>
       <c r="B128">
         <v>48</v>
       </c>
       <c r="C128" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D128" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E128" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -8107,40 +7928,40 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q128" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R128" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T128" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>128</v>
       </c>
       <c r="B129">
         <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D129" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E129" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -8161,40 +7982,40 @@
         <v>0</v>
       </c>
       <c r="L129" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T129" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A130:A151" si="4">ROW()-1</f>
         <v>129</v>
       </c>
       <c r="B130">
         <v>69</v>
       </c>
       <c r="C130" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E130" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -8215,40 +8036,40 @@
         <v>0</v>
       </c>
       <c r="L130" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T130" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131">
-        <f t="shared" ref="A131:A151" si="2">ROW()-1</f>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="B131">
         <v>52</v>
       </c>
       <c r="C131" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D131" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E131" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -8269,40 +8090,40 @@
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q131" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R131" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>131</v>
       </c>
       <c r="B132">
         <v>42</v>
       </c>
       <c r="C132" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D132" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E132" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -8311,7 +8132,7 @@
         <v>0</v>
       </c>
       <c r="H132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132">
         <v>2</v>
@@ -8323,40 +8144,40 @@
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q132" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R132" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T132" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>132</v>
       </c>
       <c r="B133">
         <v>112</v>
       </c>
       <c r="C133" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D133" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E133" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -8377,40 +8198,40 @@
         <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T133" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>133</v>
       </c>
       <c r="B134">
         <v>51</v>
       </c>
       <c r="C134" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D134" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E134" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -8431,43 +8252,43 @@
         <v>1</v>
       </c>
       <c r="L134" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M134">
         <v>2</v>
       </c>
       <c r="N134" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T134" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>134</v>
       </c>
       <c r="B135">
         <v>61</v>
       </c>
       <c r="C135" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E135" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -8488,40 +8309,40 @@
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M135" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q135" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R135" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S135" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T135" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>135</v>
       </c>
       <c r="B136">
         <v>14</v>
       </c>
       <c r="C136" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D136" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E136" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -8542,40 +8363,40 @@
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T136" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>136</v>
       </c>
       <c r="B137">
         <v>10</v>
       </c>
       <c r="C137" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D137" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E137" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -8596,40 +8417,40 @@
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M137" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q137" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R137" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S137" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T137" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>137</v>
       </c>
       <c r="B138">
         <v>106</v>
       </c>
       <c r="C138" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D138" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E138" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -8644,46 +8465,46 @@
         <v>0</v>
       </c>
       <c r="J138">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K138">
         <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T138" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>138</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D139" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E139" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -8704,40 +8525,40 @@
         <v>0</v>
       </c>
       <c r="L139" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q139" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R139" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="S139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T139" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>139</v>
       </c>
       <c r="B140">
         <v>31</v>
       </c>
       <c r="C140" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D140" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E140" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -8758,40 +8579,40 @@
         <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T140" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="B141">
         <v>45</v>
       </c>
       <c r="C141" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D141" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E141" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -8812,40 +8633,40 @@
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T141" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>141</v>
       </c>
       <c r="B142">
         <v>24</v>
       </c>
       <c r="C142" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D142" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E142" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -8866,43 +8687,43 @@
         <v>0</v>
       </c>
       <c r="L142" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M142">
         <v>9</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T142" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>142</v>
       </c>
       <c r="B143">
         <v>40</v>
       </c>
       <c r="C143" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D143" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E143" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -8923,40 +8744,40 @@
         <v>0</v>
       </c>
       <c r="L143" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>143</v>
       </c>
       <c r="B144">
         <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E144" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -8977,40 +8798,40 @@
         <v>0</v>
       </c>
       <c r="L144" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T144" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="B145">
         <v>30</v>
       </c>
       <c r="C145" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D145" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E145" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -9031,43 +8852,43 @@
         <v>1</v>
       </c>
       <c r="L145" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M145">
         <v>10</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T145" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>145</v>
       </c>
       <c r="B146">
         <v>47</v>
       </c>
       <c r="C146" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D146" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E146" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -9076,7 +8897,7 @@
         <v>0</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146">
         <v>4</v>
@@ -9088,40 +8909,40 @@
         <v>0</v>
       </c>
       <c r="L146" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q146" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R146" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="S146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T146" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>146</v>
       </c>
       <c r="B147">
         <v>118</v>
       </c>
       <c r="C147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D147" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E147" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -9142,40 +8963,40 @@
         <v>1</v>
       </c>
       <c r="L147" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T147" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="148" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>147</v>
       </c>
       <c r="B148">
         <v>115</v>
       </c>
       <c r="C148" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E148" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -9196,40 +9017,40 @@
         <v>0</v>
       </c>
       <c r="L148" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T148" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>148</v>
       </c>
       <c r="B149">
         <v>85</v>
       </c>
       <c r="C149" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D149" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E149" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -9244,46 +9065,46 @@
         <v>0</v>
       </c>
       <c r="J149">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K149">
         <v>0</v>
       </c>
       <c r="L149" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>149</v>
       </c>
       <c r="B150">
         <v>61</v>
       </c>
       <c r="C150" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E150" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -9304,40 +9125,40 @@
         <v>0</v>
       </c>
       <c r="L150" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T150" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="B151">
         <v>24</v>
       </c>
       <c r="C151" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D151" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E151" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -9358,28 +9179,29 @@
         <v>0</v>
       </c>
       <c r="L151" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M151">
         <v>1</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q151" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R151" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S151" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T151" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>